--- a/src/test_data/data.xlsx
+++ b/src/test_data/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\VSCODE\Playwright_Automation_TS\src\test_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\VSCODE\Playwright_Automation_TS\DemoQA\src\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165B5B5B-8DD3-42E6-B731-8EB6EFE6FB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751B2F10-31A0-4243-A84A-BED4761BF5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1120CC49-D95F-4BF2-BC9C-D733C0CBC652}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>TestScriptName</t>
   </si>
@@ -45,19 +45,7 @@
     <t>pPassword</t>
   </si>
   <si>
-    <t>https://rahulshettyacademy.com/loginpagePractise/</t>
-  </si>
-  <si>
     <t>chrome</t>
-  </si>
-  <si>
-    <t>rahulshettyacademy</t>
-  </si>
-  <si>
-    <t>Learning@830$3mK2</t>
-  </si>
-  <si>
-    <t>Check Login for rahulshettyacademy</t>
   </si>
   <si>
     <t>Login to DemoQA website</t>
@@ -426,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{726F6662-5AB1-4B30-B11F-301067991C44}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -458,43 +446,21 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{88ABE6A8-C495-41D3-9932-0F9247A89139}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{24EAAA17-E935-4786-BE1B-64E7EA3658A9}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{86468A09-B8DB-4889-9DE2-5470CD5DA9A2}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{86468A09-B8DB-4889-9DE2-5470CD5DA9A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
